--- a/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T11:53:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:53:44+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T12:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T12:55:48+01:00</t>
+    <t>2026-03-18T17:09:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T11:10:04+02:00</t>
+    <t>2026-06-24T16:51:19+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:51:19+02:00</t>
+    <t>2026-06-26T18:38:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T18:38:01+02:00</t>
+    <t>2026-07-06T17:54:18+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T17:54:18+02:00</t>
+    <t>2026-07-22T15:49:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-BDT-Betriebsstaettenstatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:49:40+02:00</t>
+    <t>2026-07-22T16:29:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
